--- a/314e-ig/output/StructureDefinition-careplan-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careplan-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -309,7 +309,7 @@
     <t>CarePlan.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-careplan-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careplan-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1141,8 +1141,7 @@
     <t>Applied to an individual activity element within a CarePlan resource.
 Stores the target or goal date-time for completing that specific care plan
 activity.
-Standard FHIR CarePlan.activity has no dedicated target date field separate
-from scheduledTiming or scheduledPeriod.</t>
+Note that the targetDateTime is separate from CarePlan.activity.scheduled[x].</t>
   </si>
   <si>
     <t>CarePlan.activity.modifierExtension</t>

--- a/314e-ig/output/StructureDefinition-careplan-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careplan-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-careplan-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careplan-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-careplan-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careplan-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -665,7 +665,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -844,7 +844,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -872,7 +872,7 @@
     <t>CarePlan.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -961,7 +961,7 @@
     <t>CarePlan.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|RelatedPerson|Organization|CareTeam) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/careteam-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -995,7 +995,7 @@
     <t>CarePlan.careTeam</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careteam-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1017,7 +1017,7 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1048,7 +1048,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1070,7 +1070,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/goal-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1231,7 +1231,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|MedicationRequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1373,7 +1373,7 @@
     <t>CarePlan.activity.detail.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1494,7 +1494,7 @@
     <t>CarePlan.activity.detail.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1519,7 +1519,7 @@
     <t>CarePlan.activity.detail.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|RelatedPerson|Patient|CareTeam|HealthcareService|Device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1961,7 +1961,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="176.953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-careplan-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careplan-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-careplan-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-careplan-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
